--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128479374</v>
       </c>
       <c r="B2" t="n">
-        <v>90954</v>
+        <v>90960</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128480497</v>
       </c>
       <c r="B3" t="n">
-        <v>91748</v>
+        <v>91754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128479841</v>
       </c>
       <c r="B4" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128479485</v>
       </c>
       <c r="B5" t="n">
-        <v>86715</v>
+        <v>86720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128479929</v>
       </c>
       <c r="B6" t="n">
-        <v>92731</v>
+        <v>92737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128479803</v>
       </c>
       <c r="B7" t="n">
-        <v>92741</v>
+        <v>92747</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128494247</v>
       </c>
       <c r="B8" t="n">
-        <v>86860</v>
+        <v>86864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128479374</v>
       </c>
       <c r="B2" t="n">
-        <v>90960</v>
+        <v>90966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128480497</v>
       </c>
       <c r="B3" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128479841</v>
       </c>
       <c r="B4" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128479485</v>
       </c>
       <c r="B5" t="n">
-        <v>86720</v>
+        <v>86726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128479929</v>
       </c>
       <c r="B6" t="n">
-        <v>92737</v>
+        <v>92743</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128479803</v>
       </c>
       <c r="B7" t="n">
-        <v>92747</v>
+        <v>92753</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128494247</v>
       </c>
       <c r="B8" t="n">
-        <v>86864</v>
+        <v>86870</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128479374</v>
       </c>
       <c r="B2" t="n">
-        <v>90966</v>
+        <v>90968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128480497</v>
       </c>
       <c r="B3" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128479841</v>
       </c>
       <c r="B4" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128479485</v>
       </c>
       <c r="B5" t="n">
-        <v>86726</v>
+        <v>86728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128479929</v>
       </c>
       <c r="B6" t="n">
-        <v>92743</v>
+        <v>92745</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128479803</v>
       </c>
       <c r="B7" t="n">
-        <v>92753</v>
+        <v>92755</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128494247</v>
       </c>
       <c r="B8" t="n">
-        <v>86870</v>
+        <v>86872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128480497</v>
+        <v>128479841</v>
       </c>
       <c r="B3" t="n">
-        <v>91762</v>
+        <v>92768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128479841</v>
+        <v>128480497</v>
       </c>
       <c r="B4" t="n">
-        <v>92768</v>
+        <v>91762</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128479485</v>
+        <v>128479929</v>
       </c>
       <c r="B5" t="n">
-        <v>86728</v>
+        <v>92745</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>459</v>
+        <v>150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Frygisk spindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius phrygianus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633255</v>
+        <v>633239</v>
       </c>
       <c r="R5" t="n">
-        <v>6721138</v>
+        <v>6721121</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128479929</v>
+        <v>128479803</v>
       </c>
       <c r="B6" t="n">
-        <v>92745</v>
+        <v>92755</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>1435</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128479803</v>
+        <v>128494247</v>
       </c>
       <c r="B7" t="n">
-        <v>92755</v>
+        <v>86872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,24 +1171,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1435</v>
+        <v>248955</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fråganbo grustäkt, Upl</t>
@@ -1239,6 +1250,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1257,10 +1269,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128494247</v>
+        <v>128750619</v>
       </c>
       <c r="B8" t="n">
-        <v>86872</v>
+        <v>86820</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,45 +1280,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>248955</v>
+        <v>445</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kauffman</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fråganbo grustäkt, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633239</v>
+        <v>633255</v>
       </c>
       <c r="R8" t="n">
-        <v>6721121</v>
+        <v>6721138</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,7 +1348,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1363,6 +1363,103 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128479485</v>
+      </c>
+      <c r="B9" t="n">
+        <v>86728</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>459</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Frygisk spindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius phrygianus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fråganbo grustäkt, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>633255</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6721138</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128479374</v>
       </c>
       <c r="B2" t="n">
-        <v>90968</v>
+        <v>90969</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128479841</v>
+        <v>128480497</v>
       </c>
       <c r="B3" t="n">
-        <v>92768</v>
+        <v>91763</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128480497</v>
+        <v>128479841</v>
       </c>
       <c r="B4" t="n">
-        <v>91762</v>
+        <v>92769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>128479929</v>
       </c>
       <c r="B5" t="n">
-        <v>92745</v>
+        <v>92746</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128479803</v>
       </c>
       <c r="B6" t="n">
-        <v>92755</v>
+        <v>92756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128479374</v>
       </c>
       <c r="B2" t="n">
-        <v>90969</v>
+        <v>90996</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128480497</v>
+        <v>128479841</v>
       </c>
       <c r="B3" t="n">
-        <v>91763</v>
+        <v>92796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128479841</v>
+        <v>128480497</v>
       </c>
       <c r="B4" t="n">
-        <v>92769</v>
+        <v>91790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>128479929</v>
       </c>
       <c r="B5" t="n">
-        <v>92746</v>
+        <v>92773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128479803</v>
       </c>
       <c r="B6" t="n">
-        <v>92756</v>
+        <v>92783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128494247</v>
       </c>
       <c r="B7" t="n">
-        <v>86872</v>
+        <v>86899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>128750619</v>
       </c>
       <c r="B8" t="n">
-        <v>86820</v>
+        <v>86847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>128479485</v>
       </c>
       <c r="B9" t="n">
-        <v>86728</v>
+        <v>86755</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128479374</v>
       </c>
       <c r="B2" t="n">
-        <v>90996</v>
+        <v>91001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128479841</v>
+        <v>128480497</v>
       </c>
       <c r="B3" t="n">
-        <v>92796</v>
+        <v>91795</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128480497</v>
+        <v>128479841</v>
       </c>
       <c r="B4" t="n">
-        <v>91790</v>
+        <v>92801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>128479929</v>
       </c>
       <c r="B5" t="n">
-        <v>92773</v>
+        <v>92778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128479803</v>
       </c>
       <c r="B6" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128494247</v>
       </c>
       <c r="B7" t="n">
-        <v>86899</v>
+        <v>86903</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>128750619</v>
       </c>
       <c r="B8" t="n">
-        <v>86847</v>
+        <v>86851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>128479485</v>
       </c>
       <c r="B9" t="n">
-        <v>86755</v>
+        <v>86759</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128479374</v>
       </c>
       <c r="B2" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128480497</v>
+        <v>128479841</v>
       </c>
       <c r="B3" t="n">
-        <v>91795</v>
+        <v>92806</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128479841</v>
+        <v>128480497</v>
       </c>
       <c r="B4" t="n">
-        <v>92801</v>
+        <v>91800</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>128479929</v>
       </c>
       <c r="B5" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128479803</v>
       </c>
       <c r="B6" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128494247</v>
       </c>
       <c r="B7" t="n">
-        <v>86903</v>
+        <v>86904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128479374</v>
       </c>
       <c r="B2" t="n">
-        <v>91006</v>
+        <v>91010</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128479841</v>
+        <v>128480497</v>
       </c>
       <c r="B3" t="n">
-        <v>92806</v>
+        <v>91804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128480497</v>
+        <v>128479841</v>
       </c>
       <c r="B4" t="n">
-        <v>91800</v>
+        <v>92810</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>128479929</v>
       </c>
       <c r="B5" t="n">
-        <v>92783</v>
+        <v>92787</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128479803</v>
       </c>
       <c r="B6" t="n">
-        <v>92793</v>
+        <v>92797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128494247</v>
       </c>
       <c r="B7" t="n">
-        <v>86904</v>
+        <v>86908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>128750619</v>
       </c>
       <c r="B8" t="n">
-        <v>86851</v>
+        <v>86855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>128479485</v>
       </c>
       <c r="B9" t="n">
-        <v>86759</v>
+        <v>86763</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128480497</v>
+        <v>128479841</v>
       </c>
       <c r="B3" t="n">
-        <v>91804</v>
+        <v>92810</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128479841</v>
+        <v>128480497</v>
       </c>
       <c r="B4" t="n">
-        <v>92810</v>
+        <v>91804</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128479841</v>
+        <v>128480497</v>
       </c>
       <c r="B3" t="n">
-        <v>92810</v>
+        <v>91804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128480497</v>
+        <v>128479841</v>
       </c>
       <c r="B4" t="n">
-        <v>91804</v>
+        <v>92810</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128479374</v>
       </c>
       <c r="B2" t="n">
-        <v>91010</v>
+        <v>91015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128480497</v>
       </c>
       <c r="B3" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128479841</v>
       </c>
       <c r="B4" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128479929</v>
       </c>
       <c r="B5" t="n">
-        <v>92787</v>
+        <v>92792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128479803</v>
       </c>
       <c r="B6" t="n">
-        <v>92797</v>
+        <v>92802</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128494247</v>
       </c>
       <c r="B7" t="n">
-        <v>86908</v>
+        <v>86913</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>128750619</v>
       </c>
       <c r="B8" t="n">
-        <v>86855</v>
+        <v>86860</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>128479485</v>
       </c>
       <c r="B9" t="n">
-        <v>86763</v>
+        <v>86768</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128479374</v>
       </c>
       <c r="B2" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128479841</v>
+        <v>128480497</v>
       </c>
       <c r="B3" t="n">
-        <v>92818</v>
+        <v>91805</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128480497</v>
+        <v>128479841</v>
       </c>
       <c r="B4" t="n">
-        <v>91800</v>
+        <v>92823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>128479929</v>
       </c>
       <c r="B5" t="n">
-        <v>92795</v>
+        <v>92800</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128479803</v>
       </c>
       <c r="B6" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128494247</v>
       </c>
       <c r="B7" t="n">
-        <v>86915</v>
+        <v>86920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -1272,7 +1272,7 @@
         <v>128750619</v>
       </c>
       <c r="B8" t="n">
-        <v>86867</v>
+        <v>86870</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>128479485</v>
       </c>
       <c r="B9" t="n">
-        <v>86775</v>
+        <v>86778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128479374</v>
       </c>
       <c r="B2" t="n">
-        <v>91022</v>
+        <v>91028</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128480497</v>
       </c>
       <c r="B3" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128479841</v>
       </c>
       <c r="B4" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128479929</v>
       </c>
       <c r="B5" t="n">
-        <v>92800</v>
+        <v>92808</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128479803</v>
       </c>
       <c r="B6" t="n">
-        <v>92810</v>
+        <v>92818</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128494247</v>
       </c>
       <c r="B7" t="n">
-        <v>86920</v>
+        <v>86926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>128750619</v>
       </c>
       <c r="B8" t="n">
-        <v>86870</v>
+        <v>86873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>128479485</v>
       </c>
       <c r="B9" t="n">
-        <v>86778</v>
+        <v>86781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -1272,7 +1272,7 @@
         <v>128750619</v>
       </c>
       <c r="B8" t="n">
-        <v>86873</v>
+        <v>86877</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>128479485</v>
       </c>
       <c r="B9" t="n">
-        <v>86781</v>
+        <v>86785</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -1272,7 +1272,7 @@
         <v>128750619</v>
       </c>
       <c r="B8" t="n">
-        <v>86877</v>
+        <v>86884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>128479485</v>
       </c>
       <c r="B9" t="n">
-        <v>86785</v>
+        <v>86792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -1272,7 +1272,7 @@
         <v>128750619</v>
       </c>
       <c r="B8" t="n">
-        <v>86884</v>
+        <v>86886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>128479485</v>
       </c>
       <c r="B9" t="n">
-        <v>86792</v>
+        <v>86794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -1272,7 +1272,7 @@
         <v>128750619</v>
       </c>
       <c r="B8" t="n">
-        <v>86886</v>
+        <v>86887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>128479485</v>
       </c>
       <c r="B9" t="n">
-        <v>86794</v>
+        <v>86795</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128479374</v>
+        <v>128479929</v>
       </c>
       <c r="B2" t="n">
-        <v>91028</v>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>256703</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633269</v>
+        <v>633239</v>
       </c>
       <c r="R2" t="n">
-        <v>6721179</v>
+        <v>6721121</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128480497</v>
+        <v>128750619</v>
       </c>
       <c r="B3" t="n">
-        <v>91811</v>
+        <v>87238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>445</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633239</v>
+        <v>633255</v>
       </c>
       <c r="R3" t="n">
-        <v>6721121</v>
+        <v>6721138</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128479841</v>
+        <v>128479485</v>
       </c>
       <c r="B4" t="n">
-        <v>92831</v>
+        <v>87145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>459</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Frygisk spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius phrygianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633239</v>
+        <v>633255</v>
       </c>
       <c r="R4" t="n">
-        <v>6721121</v>
+        <v>6721138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128479929</v>
+        <v>128480497</v>
       </c>
       <c r="B5" t="n">
-        <v>92808</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,11 +1066,11 @@
         <v>128479803</v>
       </c>
       <c r="B6" t="n">
-        <v>92818</v>
+        <v>93196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1160,46 +1160,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494247</v>
+        <v>128479841</v>
       </c>
       <c r="B7" t="n">
-        <v>86926</v>
+        <v>93209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>248955</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Kauffman</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fråganbo grustäkt, Upl</t>
@@ -1250,7 +1239,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1269,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128750619</v>
+        <v>15730020</v>
       </c>
       <c r="B8" t="n">
-        <v>86887</v>
+        <v>45044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,34 +1268,53 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>445</v>
+        <v>102018</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fråganbo grustäkt, Upl</t>
+          <t>Älvboda, vägkant i norr på Västanåvägen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633255</v>
+        <v>633283</v>
       </c>
       <c r="R8" t="n">
-        <v>6721138</v>
+        <v>6721212</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1334,12 +1341,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2013-06-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2013-06-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3 ex.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1351,60 +1363,85 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gräsmark på kalkrikt underlag</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Via Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128479485</v>
+        <v>15730024</v>
       </c>
       <c r="B9" t="n">
-        <v>86795</v>
+        <v>45049</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>459</v>
+        <v>102021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Frygisk spindling</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius phrygianus</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fråganbo grustäkt, Upl</t>
+          <t>Älvboda, vägkant i norr på Västanåvägen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633255</v>
+        <v>633300</v>
       </c>
       <c r="R9" t="n">
-        <v>6721138</v>
+        <v>6721187</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1431,12 +1468,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2013-06-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2013-06-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1448,18 +1490,608 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Gräsmark på kalkrikt underlag</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>15730009</v>
+      </c>
+      <c r="B10" t="n">
+        <v>45042</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>201164</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Zygaena filipendulae</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Älvboda, vägkant i norr på Västanåvägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>633283</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6721212</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2013-06-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2013-06-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1 ex.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gräsmark på kalkrikt underlag</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>15730011</v>
+      </c>
+      <c r="B11" t="n">
+        <v>45042</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>201164</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Zygaena filipendulae</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Älvboda, vägkant i norr på Västanåvägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>633295</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6721210</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2013-06-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2013-06-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>5 ex. 2 parningar.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Gräsmark på kalkrikt underlag</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>101771661</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Västanåvägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>633299</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6721182</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128494247</v>
+      </c>
+      <c r="B13" t="n">
+        <v>87291</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fråganbo grustäkt, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>633239</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6721121</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Anton Björk</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Anton Björk</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128479374</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fråganbo grustäkt, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>633269</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6721179</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -1257,64 +1257,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15730020</v>
+        <v>128479374</v>
       </c>
       <c r="B8" t="n">
-        <v>45044</v>
+        <v>91474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102018</v>
+        <v>5741</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Älvboda, vägkant i norr på Västanåvägen, Upl</t>
+          <t>Fråganbo grustäkt, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633283</v>
+        <v>633269</v>
       </c>
       <c r="R8" t="n">
-        <v>6721212</v>
+        <v>6721179</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1341,17 +1333,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2013-06-18</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-06-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>3 ex.</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1360,34 +1347,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Gräsmark på kalkrikt underlag</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Thure Nordin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Lars-Thure Nordin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>15730024</v>
+        <v>15730020</v>
       </c>
       <c r="B9" t="n">
-        <v>45049</v>
+        <v>45044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,26 +1377,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102021</v>
+        <v>102018</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1438,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633300</v>
+        <v>633283</v>
       </c>
       <c r="R9" t="n">
-        <v>6721187</v>
+        <v>6721212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,7 +1460,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>3 ex.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1493,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>15730009</v>
+        <v>15730024</v>
       </c>
       <c r="B10" t="n">
-        <v>45042</v>
+        <v>45049</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,26 +1504,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>201164</v>
+        <v>102021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1565,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633283</v>
+        <v>633300</v>
       </c>
       <c r="R10" t="n">
-        <v>6721212</v>
+        <v>6721187</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1605,7 +1587,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1 ex.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1620,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>15730011</v>
+        <v>15730009</v>
       </c>
       <c r="B11" t="n">
         <v>45042</v>
@@ -1668,7 +1650,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1692,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633295</v>
+        <v>633283</v>
       </c>
       <c r="R11" t="n">
-        <v>6721210</v>
+        <v>6721212</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1714,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>5 ex. 2 parningar.</t>
+          <t>1 ex.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,61 +1747,64 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101771661</v>
+        <v>15730011</v>
       </c>
       <c r="B12" t="n">
-        <v>99153</v>
+        <v>45042</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>201164</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västanåvägen, Upl</t>
+          <t>Älvboda, vägkant i norr på Västanåvägen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633299</v>
+        <v>633295</v>
       </c>
       <c r="R12" t="n">
-        <v>6721182</v>
+        <v>6721210</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,22 +1831,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2013-06-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2013-06-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>5 ex. 2 parningar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,75 +1850,85 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gräsmark på kalkrikt underlag</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Via Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128494247</v>
+        <v>101771661</v>
       </c>
       <c r="B13" t="n">
-        <v>87291</v>
+        <v>99153</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>248955</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fråganbo grustäkt, Upl</t>
+          <t>Västanåvägen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633239</v>
+        <v>633299</v>
       </c>
       <c r="R13" t="n">
-        <v>6721121</v>
+        <v>6721182</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,12 +1955,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1986,57 +1986,68 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128479374</v>
+        <v>128494247</v>
       </c>
       <c r="B14" t="n">
-        <v>91402</v>
+        <v>87291</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>256703</v>
+        <v>248955</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fråganbo grustäkt, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633269</v>
+        <v>633239</v>
       </c>
       <c r="R14" t="n">
-        <v>6721179</v>
+        <v>6721121</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,6 +2088,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128479929</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128750619</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128479485</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128480497</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128479803</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128479841</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128479374</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15730020</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15730024</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1744,6 +1794,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15730009</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1871,6 +1926,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15730011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1995,6 +2055,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101771661</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2104,8 +2169,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494247</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>128479374</v>
       </c>
       <c r="B8" t="n">
-        <v>91474</v>
+        <v>91516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>128479374</v>
       </c>
       <c r="B8" t="n">
-        <v>91516</v>
+        <v>91543</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1292,64 +1292,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15730020</v>
+        <v>128479374</v>
       </c>
       <c r="B8" t="n">
-        <v>45044</v>
+        <v>91546</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102018</v>
+        <v>5741</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Älvboda, vägkant i norr på Västanåvägen, Upl</t>
+          <t>Fråganbo grustäkt, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633283</v>
+        <v>633269</v>
       </c>
       <c r="R8" t="n">
-        <v>6721212</v>
+        <v>6721179</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1376,17 +1368,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2013-06-18</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-06-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>3 ex.</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1395,39 +1382,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Gräsmark på kalkrikt underlag</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Thure Nordin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Lars-Thure Nordin</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15730020</t>
+          <t>https://artportalen.se/Sighting/128479374</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>15730024</v>
+        <v>15730020</v>
       </c>
       <c r="B9" t="n">
-        <v>45049</v>
+        <v>45044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,26 +1417,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102021</v>
+        <v>102018</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1478,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633300</v>
+        <v>633283</v>
       </c>
       <c r="R9" t="n">
-        <v>6721187</v>
+        <v>6721212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1500,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>3 ex.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,16 +1532,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15730024</t>
+          <t>https://artportalen.se/Sighting/15730020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>15730009</v>
+        <v>15730024</v>
       </c>
       <c r="B10" t="n">
-        <v>45042</v>
+        <v>45049</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,26 +1549,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>201164</v>
+        <v>102021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1610,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633283</v>
+        <v>633300</v>
       </c>
       <c r="R10" t="n">
-        <v>6721212</v>
+        <v>6721187</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1632,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1 ex.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,13 +1664,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15730009</t>
+          <t>https://artportalen.se/Sighting/15730024</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>15730011</v>
+        <v>15730009</v>
       </c>
       <c r="B11" t="n">
         <v>45042</v>
@@ -1718,7 +1700,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1742,10 +1724,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633295</v>
+        <v>633283</v>
       </c>
       <c r="R11" t="n">
-        <v>6721210</v>
+        <v>6721212</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1764,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>5 ex. 2 parningar.</t>
+          <t>1 ex.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,67 +1796,70 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15730011</t>
+          <t>https://artportalen.se/Sighting/15730009</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101771661</v>
+        <v>15730011</v>
       </c>
       <c r="B12" t="n">
-        <v>99153</v>
+        <v>45042</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>201164</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västanåvägen, Upl</t>
+          <t>Älvboda, vägkant i norr på Västanåvägen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633299</v>
+        <v>633295</v>
       </c>
       <c r="R12" t="n">
-        <v>6721182</v>
+        <v>6721210</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,22 +1886,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2013-06-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2013-06-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>5 ex. 2 parningar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,80 +1905,90 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gräsmark på kalkrikt underlag</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Via Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101771661</t>
+          <t>https://artportalen.se/Sighting/15730011</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128494247</v>
+        <v>101771661</v>
       </c>
       <c r="B13" t="n">
-        <v>87291</v>
+        <v>99153</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>248955</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fråganbo grustäkt, Upl</t>
+          <t>Västanåvägen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633239</v>
+        <v>633299</v>
       </c>
       <c r="R13" t="n">
-        <v>6721121</v>
+        <v>6721182</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,12 +2015,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,16 +2046,130 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101771661</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128494247</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87291</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fråganbo grustäkt, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>633239</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6721121</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128494247</t>
         </is>
@@ -2075,6 +2189,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27330-2025 artfynd.xlsx
+++ b/artfynd/A 27330-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>128479374</v>
       </c>
       <c r="B8" t="n">
-        <v>91546</v>
+        <v>91548</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
